--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.77998102494841</v>
+        <v>5.326746916554116</v>
       </c>
       <c r="D2" t="n">
-        <v>32.11627049816126</v>
+        <v>5.218893955951206</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F2" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.24928327719918</v>
+        <v>4.753008532544867</v>
       </c>
       <c r="D3" t="n">
-        <v>29.39277521824759</v>
+        <v>4.776325972965233</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F3" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.94467680921487</v>
+        <v>6.166009981497417</v>
       </c>
       <c r="D4" t="n">
-        <v>37.83741111437331</v>
+        <v>6.148579306085663</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F4" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>2.486557317169941</v>
+        <v>0.4040655640401154</v>
       </c>
       <c r="D5" t="n">
-        <v>2.495815433791576</v>
+        <v>0.4055700079911311</v>
       </c>
       <c r="E5" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F5" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.37581440259178</v>
+        <v>4.448569840421164</v>
       </c>
       <c r="D6" t="n">
-        <v>27.43167168251296</v>
+        <v>4.457646648408356</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F6" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.59519230779012</v>
+        <v>3.671718750015895</v>
       </c>
       <c r="D7" t="n">
-        <v>22.47732462497295</v>
+        <v>3.652565251558105</v>
       </c>
       <c r="E7" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F7" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.71538181450352</v>
+        <v>5.803749544856822</v>
       </c>
       <c r="D8" t="n">
-        <v>35.67410484888948</v>
+        <v>5.79704203794454</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F8" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.99504208694358</v>
+        <v>6.824194339128333</v>
       </c>
       <c r="D9" t="n">
-        <v>41.80692974528862</v>
+        <v>6.793626083609401</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F9" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.24303620797638</v>
+        <v>7.351993383796162</v>
       </c>
       <c r="D10" t="n">
-        <v>45.06666892163786</v>
+        <v>7.323333699766153</v>
       </c>
       <c r="E10" t="n">
-        <v>11.9990351850392</v>
+        <v>1.94984321756887</v>
       </c>
       <c r="F10" t="n">
-        <v>11.93728782445569</v>
+        <v>1.93980927147405</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
